--- a/assets/constructions/examples/ctd_mb2.xlsx
+++ b/assets/constructions/examples/ctd_mb2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AV6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -644,21 +644,46 @@
           <t>cpdf</t>
         </is>
       </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>G8A28055</t>
+          <t>R216.42-00230-IC02G 1700</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>YG1</t>
+          <t>SANDVIK</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>G8A28</t>
+          <t>CoroMillⓇ Plura solid carbide ball nose end mill for micro-milling</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -666,26 +691,22 @@
           <t>H</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>5.5</v>
+        <v>0.2</v>
       </c>
       <c r="G2" t="n">
-        <v>2.75</v>
+        <v>0.1</v>
       </c>
       <c r="H2" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
         <v>2</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>HA-6</t>
+          <t>HA-4</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -693,16 +714,12 @@
           <t>WORKPIECE</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>0/-0,012</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>6.5</v>
+        <v>0.15</v>
       </c>
       <c r="N2" t="n">
-        <v>6.5</v>
+        <v>0.15</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -711,38 +728,46 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>h6</t>
+          <t>h5</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Nano Grain Carbide</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="S2" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>Blue-Coating</t>
+          <t>PVD ALCRN</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>COROMANT</t>
+        </is>
+      </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="Y2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="n">
-        <v>5.35</v>
+        <v>0.17</v>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
@@ -751,17 +776,27 @@
       <c r="AG2" t="n">
         <v>30</v>
       </c>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
+      <c r="AH2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>80000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.012</v>
+      </c>
       <c r="AM2" t="n">
         <v>0</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2017 - YG1 - General catalogue</t>
+          <t>2021/www.sandvik.coromant.com</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -774,12 +809,23 @@
       </c>
       <c r="AQ2" t="b">
         <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VFR2SBFR0100</t>
+          <t>VF2XLBSR0050N040</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -789,7 +835,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VFR2SBF</t>
+          <t>VF2XLBS</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -797,12 +843,16 @@
           <t>PH</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H3" t="n">
         <v>4</v>
@@ -812,7 +862,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>HA-6</t>
+          <t>HA-4</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -820,12 +870,16 @@
           <t>WORKPIECE</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0/-0,02</t>
+        </is>
+      </c>
       <c r="M3" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -835,12 +889,12 @@
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr">
         <is>
-          <t>VFR</t>
+          <t>IMPACT MIRACLE</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -849,15 +903,15 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="Y3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="n">
-        <v>1.9</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
@@ -892,37 +946,52 @@
       <c r="AQ3" t="b">
         <v>0</v>
       </c>
+      <c r="AR3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>PSH</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MLBD2.0-20-3,0-04-50-2</t>
+          <t>VF2XLBR0050N120S04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LIKON</t>
+          <t>MITSUBISHI</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MMBR-2</t>
+          <t>VF2XLB</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>HK</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>PH</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
@@ -937,12 +1006,16 @@
           <t>WORKPIECE</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0/-0,02</t>
+        </is>
+      </c>
       <c r="M4" t="n">
-        <v>0.15</v>
+        <v>0.8</v>
       </c>
       <c r="N4" t="n">
-        <v>0.15</v>
+        <v>0.8</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -952,12 +1025,12 @@
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>0.15</v>
+        <v>0.8</v>
       </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr">
         <is>
-          <t>AlTiN</t>
+          <t>IMPACT MIRACLE</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -973,15 +1046,17 @@
       </c>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="n">
-        <v>20</v>
-      </c>
+      <c r="AB4" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
+      <c r="AF4" t="n">
+        <v>12</v>
+      </c>
       <c r="AG4" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr"/>
@@ -993,7 +1068,7 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2022/LIKON Инструментальный каталог</t>
+          <t>2020 / Mitsubishi Website</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1006,12 +1081,23 @@
       </c>
       <c r="AQ4" t="b">
         <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>PSH</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SEM846008106SE</t>
+          <t>SEME560202030</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1021,30 +1107,30 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SEM84</t>
+          <t>SEME56</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MKH</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="I5" t="n">
         <v>2</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>HA-6</t>
+          <t>HA-4</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1058,10 +1144,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1079,7 +1165,7 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr">
@@ -1093,10 +1179,10 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="Y5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
@@ -1118,7 +1204,7 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2017 - YG1 - YE-4G13</t>
+          <t>2020: www.yg1.co.kr/toolselection/main/</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -1131,45 +1217,56 @@
       </c>
       <c r="AQ5" t="b">
         <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SEM846015106SE</t>
+          <t>EB-A2 10-10/20C10H100 IC903</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>YG1</t>
+          <t>ISCAR</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SEM84</t>
+          <t>EB-A2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MKH</t>
+          <t>PMKSH</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>1.5</v>
+        <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>0.75</v>
+        <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I6" t="n">
         <v>2</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>HA-6</t>
+          <t>HA-10</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1177,39 +1274,31 @@
           <t>WORKPIECE</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>0/-0,012</t>
-        </is>
-      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>1.5</v>
+        <v>10</v>
       </c>
       <c r="N6" t="n">
-        <v>1.5</v>
+        <v>10</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
           <t>HA</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>h6</t>
-        </is>
-      </c>
+      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Nano Grain Carbide</t>
+          <t>IC903</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>1.5</v>
+        <v>10</v>
       </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr">
         <is>
-          <t>Y-Coating</t>
+          <t>TiAlN</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1218,14 +1307,16 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Y6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
+      <c r="AB6" t="n">
+        <v>9.9</v>
+      </c>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
@@ -1243,7 +1334,7 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2017 - YG1 - YE-4G13</t>
+          <t>2019/rotation-toos-2019-milling-tools.pdf</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -1256,6 +1347,17 @@
       </c>
       <c r="AQ6" t="b">
         <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>PMKSH</t>
+        </is>
       </c>
     </row>
   </sheetData>
